--- a/QUOTATION.xlsx
+++ b/QUOTATION.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">         Quotation</t>
   </si>
@@ -127,10 +127,7 @@
     <t xml:space="preserve"> For,    CORPORATEMART PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>Authorised Signatory</t>
-  </si>
-  <si>
-    <t>We appreciate your business and look forward to work with you.</t>
+    <t>This is a system-generated quotation and does not require a signature.</t>
   </si>
 </sst>
 </file>
@@ -144,7 +141,7 @@
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,13 +257,6 @@
       <name val="Cambria"/>
       <charset val="134"/>
       <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -964,146 +954,146 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1401,9 +1391,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>943993</xdr:colOff>
+      <xdr:colOff>1214755</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>752475</xdr:rowOff>
+      <xdr:rowOff>988060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1427,8 +1417,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="6972300"/>
-          <a:ext cx="1766570" cy="1537335"/>
+          <a:off x="9525" y="6979920"/>
+          <a:ext cx="2037715" cy="1772920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1474,7 +1464,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28575" y="428625"/>
-          <a:ext cx="2518410" cy="401955"/>
+          <a:ext cx="2518410" cy="409575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1790,7 +1780,7 @@
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" ht="14.55" spans="1:4">
+    <row r="2" ht="15.15" spans="1:4">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2043,17 +2033,15 @@
       <c r="C36" s="65"/>
       <c r="D36" s="66"/>
     </row>
-    <row r="37" ht="63" customHeight="1" spans="1:4">
-      <c r="A37" s="67" t="s">
-        <v>22</v>
-      </c>
+    <row r="37" ht="78" customHeight="1" spans="1:4">
+      <c r="A37" s="67"/>
       <c r="B37" s="68"/>
       <c r="C37" s="68"/>
       <c r="D37" s="69"/>
     </row>
     <row r="38" ht="25.5" customHeight="1" spans="1:4">
       <c r="A38" s="70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B38" s="71"/>
       <c r="C38" s="71"/>
